--- a/public/assets/template/tgr-template.xlsx
+++ b/public/assets/template/tgr-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndejo\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndejo\Documents\GitHub\simaps-ukasya\public\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEED801C-B5DA-4F5C-8CC3-ECC40E8F53EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81970E50-9D51-4D94-AD58-838A3FC1B62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="15375" windowHeight="7875" xr2:uid="{51F6D04B-38A7-4907-901E-8D2AF0D93E74}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{51F6D04B-38A7-4907-901E-8D2AF0D93E74}"/>
   </bookViews>
   <sheets>
     <sheet name="Lembar1" sheetId="1" r:id="rId1"/>
@@ -87,15 +87,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -103,13 +109,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -427,43 +453,45 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/public/assets/template/tgr-template.xlsx
+++ b/public/assets/template/tgr-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndejo\Documents\GitHub\simaps-ukasya\public\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81970E50-9D51-4D94-AD58-838A3FC1B62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B2C421-8150-4A8A-925F-1037C229DD54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{51F6D04B-38A7-4907-901E-8D2AF0D93E74}"/>
   </bookViews>
@@ -36,9 +36,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>Laki-laki</t>
-  </si>
-  <si>
     <t>Nama</t>
   </si>
   <si>
@@ -64,6 +61,9 @@
   </si>
   <si>
     <t>Ukasya</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
 </sst>
 </file>
@@ -463,36 +463,36 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/public/assets/template/tgr-template.xlsx
+++ b/public/assets/template/tgr-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndejo\Documents\GitHub\simaps-ukasya\public\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B2C421-8150-4A8A-925F-1037C229DD54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{714E2FA5-8477-4741-9DA7-08DB0B1C0566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{51F6D04B-38A7-4907-901E-8D2AF0D93E74}"/>
+    <workbookView xWindow="1860" yWindow="1860" windowWidth="15375" windowHeight="7875" xr2:uid="{51F6D04B-38A7-4907-901E-8D2AF0D93E74}"/>
   </bookViews>
   <sheets>
     <sheet name="Lembar1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>Nama</t>
   </si>
@@ -57,13 +57,16 @@
     <t>Tunggal</t>
   </si>
   <si>
-    <t>Partai A</t>
-  </si>
-  <si>
     <t>Ukasya</t>
   </si>
   <si>
     <t>L</t>
+  </si>
+  <si>
+    <t>ASAD</t>
+  </si>
+  <si>
+    <t>Mustavid</t>
   </si>
 </sst>
 </file>
@@ -450,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A86521A1-DC6B-4F40-AA0D-147BEF52CF9B}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -480,18 +483,35 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
